--- a/customers/mohammad javad.xlsx
+++ b/customers/mohammad javad.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="203">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -642,6 +642,12 @@
   </si>
   <si>
     <t>بستنی ذغال</t>
+  </si>
+  <si>
+    <t>1405/07/06</t>
+  </si>
+  <si>
+    <t>مداد پاک کن</t>
   </si>
 </sst>
 </file>
@@ -1168,7 +1174,7 @@
       </c>
       <c r="H2" s="8">
         <f>B187</f>
-        <v>1468500</v>
+        <v>1538500</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3474,17 +3480,23 @@
     <row r="166" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="7">
         <f>A165+B166-C166</f>
-        <v>1468500</v>
-      </c>
-      <c r="B166" s="7"/>
+        <v>1538500</v>
+      </c>
+      <c r="B166" s="7">
+        <v>70000</v>
+      </c>
       <c r="C166" s="7"/>
-      <c r="D166" s="7"/>
-      <c r="E166" s="1"/>
+      <c r="D166" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="167" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="7">
         <f>A166+B167-C167</f>
-        <v>1468500</v>
+        <v>1538500</v>
       </c>
       <c r="B167" s="7"/>
       <c r="C167" s="7"/>
@@ -3494,7 +3506,7 @@
     <row r="168" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="7">
         <f>A167+B168-C168</f>
-        <v>1468500</v>
+        <v>1538500</v>
       </c>
       <c r="B168" s="7"/>
       <c r="C168" s="7"/>
@@ -3504,7 +3516,7 @@
     <row r="169" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="7">
         <f>A168+B169-C169</f>
-        <v>1468500</v>
+        <v>1538500</v>
       </c>
       <c r="B169" s="7"/>
       <c r="C169" s="7"/>
@@ -3514,7 +3526,7 @@
     <row r="170" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="7">
         <f t="shared" ref="A170" si="8">A169+B170-C170</f>
-        <v>1468500</v>
+        <v>1538500</v>
       </c>
       <c r="B170" s="7"/>
       <c r="C170" s="7"/>
@@ -3524,7 +3536,7 @@
     <row r="171" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="7">
         <f>A170+B171-C171</f>
-        <v>1468500</v>
+        <v>1538500</v>
       </c>
       <c r="B171" s="7"/>
       <c r="C171" s="7"/>
@@ -3534,7 +3546,7 @@
     <row r="172" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="7">
         <f t="shared" ref="A172:A184" si="9">A171+B172-C172</f>
-        <v>1468500</v>
+        <v>1538500</v>
       </c>
       <c r="B172" s="7"/>
       <c r="C172" s="7"/>
@@ -3544,7 +3556,7 @@
     <row r="173" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="7">
         <f t="shared" si="9"/>
-        <v>1468500</v>
+        <v>1538500</v>
       </c>
       <c r="B173" s="7"/>
       <c r="C173" s="7"/>
@@ -3554,7 +3566,7 @@
     <row r="174" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="7">
         <f t="shared" si="9"/>
-        <v>1468500</v>
+        <v>1538500</v>
       </c>
       <c r="B174" s="7"/>
       <c r="C174" s="7"/>
@@ -3564,7 +3576,7 @@
     <row r="175" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="7">
         <f t="shared" si="9"/>
-        <v>1468500</v>
+        <v>1538500</v>
       </c>
       <c r="B175" s="7"/>
       <c r="C175" s="7"/>
@@ -3574,7 +3586,7 @@
     <row r="176" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="7">
         <f t="shared" si="9"/>
-        <v>1468500</v>
+        <v>1538500</v>
       </c>
       <c r="B176" s="7"/>
       <c r="C176" s="7"/>
@@ -3584,7 +3596,7 @@
     <row r="177" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="7">
         <f t="shared" si="9"/>
-        <v>1468500</v>
+        <v>1538500</v>
       </c>
       <c r="B177" s="7"/>
       <c r="C177" s="7"/>
@@ -3594,7 +3606,7 @@
     <row r="178" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="7">
         <f t="shared" si="9"/>
-        <v>1468500</v>
+        <v>1538500</v>
       </c>
       <c r="B178" s="7"/>
       <c r="C178" s="7"/>
@@ -3604,7 +3616,7 @@
     <row r="179" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="7">
         <f t="shared" si="9"/>
-        <v>1468500</v>
+        <v>1538500</v>
       </c>
       <c r="B179" s="7"/>
       <c r="C179" s="7"/>
@@ -3614,7 +3626,7 @@
     <row r="180" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="7">
         <f t="shared" si="9"/>
-        <v>1468500</v>
+        <v>1538500</v>
       </c>
       <c r="B180" s="7"/>
       <c r="C180" s="7"/>
@@ -3624,7 +3636,7 @@
     <row r="181" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="7">
         <f t="shared" si="9"/>
-        <v>1468500</v>
+        <v>1538500</v>
       </c>
       <c r="B181" s="7"/>
       <c r="C181" s="7"/>
@@ -3634,7 +3646,7 @@
     <row r="182" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="7">
         <f t="shared" si="9"/>
-        <v>1468500</v>
+        <v>1538500</v>
       </c>
       <c r="B182" s="7"/>
       <c r="C182" s="7"/>
@@ -3644,7 +3656,7 @@
     <row r="183" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="7">
         <f t="shared" si="9"/>
-        <v>1468500</v>
+        <v>1538500</v>
       </c>
       <c r="B183" s="7"/>
       <c r="C183" s="7"/>
@@ -3654,7 +3666,7 @@
     <row r="184" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="7">
         <f t="shared" si="9"/>
-        <v>1468500</v>
+        <v>1538500</v>
       </c>
       <c r="B184" s="7"/>
       <c r="C184" s="7"/>
@@ -3665,7 +3677,7 @@
       <c r="A185" s="8"/>
       <c r="B185" s="8">
         <f>SUM(B165:B184)+B159</f>
-        <v>13883500</v>
+        <v>13953500</v>
       </c>
       <c r="C185" s="8">
         <f>SUM(C165:C184)+C159</f>
@@ -3677,7 +3689,7 @@
     <row r="187" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B187" s="11">
         <f>A184</f>
-        <v>1468500</v>
+        <v>1538500</v>
       </c>
       <c r="C187" s="14" t="s">
         <v>183</v>

--- a/customers/mohammad javad.xlsx
+++ b/customers/mohammad javad.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="204">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -648,6 +648,9 @@
   </si>
   <si>
     <t>مداد پاک کن</t>
+  </si>
+  <si>
+    <t>آب</t>
   </si>
 </sst>
 </file>
@@ -1174,7 +1177,7 @@
       </c>
       <c r="H2" s="8">
         <f>B187</f>
-        <v>1538500</v>
+        <v>1583500</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3496,17 +3499,21 @@
     <row r="167" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="7">
         <f>A166+B167-C167</f>
-        <v>1538500</v>
-      </c>
-      <c r="B167" s="7"/>
+        <v>1583500</v>
+      </c>
+      <c r="B167" s="7">
+        <v>45000</v>
+      </c>
       <c r="C167" s="7"/>
-      <c r="D167" s="7"/>
+      <c r="D167" s="7" t="s">
+        <v>203</v>
+      </c>
       <c r="E167" s="1"/>
     </row>
     <row r="168" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="7">
         <f>A167+B168-C168</f>
-        <v>1538500</v>
+        <v>1583500</v>
       </c>
       <c r="B168" s="7"/>
       <c r="C168" s="7"/>
@@ -3516,7 +3523,7 @@
     <row r="169" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="7">
         <f>A168+B169-C169</f>
-        <v>1538500</v>
+        <v>1583500</v>
       </c>
       <c r="B169" s="7"/>
       <c r="C169" s="7"/>
@@ -3526,7 +3533,7 @@
     <row r="170" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="7">
         <f t="shared" ref="A170" si="8">A169+B170-C170</f>
-        <v>1538500</v>
+        <v>1583500</v>
       </c>
       <c r="B170" s="7"/>
       <c r="C170" s="7"/>
@@ -3536,7 +3543,7 @@
     <row r="171" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="7">
         <f>A170+B171-C171</f>
-        <v>1538500</v>
+        <v>1583500</v>
       </c>
       <c r="B171" s="7"/>
       <c r="C171" s="7"/>
@@ -3546,7 +3553,7 @@
     <row r="172" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="7">
         <f t="shared" ref="A172:A184" si="9">A171+B172-C172</f>
-        <v>1538500</v>
+        <v>1583500</v>
       </c>
       <c r="B172" s="7"/>
       <c r="C172" s="7"/>
@@ -3556,7 +3563,7 @@
     <row r="173" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="7">
         <f t="shared" si="9"/>
-        <v>1538500</v>
+        <v>1583500</v>
       </c>
       <c r="B173" s="7"/>
       <c r="C173" s="7"/>
@@ -3566,7 +3573,7 @@
     <row r="174" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="7">
         <f t="shared" si="9"/>
-        <v>1538500</v>
+        <v>1583500</v>
       </c>
       <c r="B174" s="7"/>
       <c r="C174" s="7"/>
@@ -3576,7 +3583,7 @@
     <row r="175" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="7">
         <f t="shared" si="9"/>
-        <v>1538500</v>
+        <v>1583500</v>
       </c>
       <c r="B175" s="7"/>
       <c r="C175" s="7"/>
@@ -3586,7 +3593,7 @@
     <row r="176" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="7">
         <f t="shared" si="9"/>
-        <v>1538500</v>
+        <v>1583500</v>
       </c>
       <c r="B176" s="7"/>
       <c r="C176" s="7"/>
@@ -3596,7 +3603,7 @@
     <row r="177" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="7">
         <f t="shared" si="9"/>
-        <v>1538500</v>
+        <v>1583500</v>
       </c>
       <c r="B177" s="7"/>
       <c r="C177" s="7"/>
@@ -3606,7 +3613,7 @@
     <row r="178" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="7">
         <f t="shared" si="9"/>
-        <v>1538500</v>
+        <v>1583500</v>
       </c>
       <c r="B178" s="7"/>
       <c r="C178" s="7"/>
@@ -3616,7 +3623,7 @@
     <row r="179" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="7">
         <f t="shared" si="9"/>
-        <v>1538500</v>
+        <v>1583500</v>
       </c>
       <c r="B179" s="7"/>
       <c r="C179" s="7"/>
@@ -3626,7 +3633,7 @@
     <row r="180" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="7">
         <f t="shared" si="9"/>
-        <v>1538500</v>
+        <v>1583500</v>
       </c>
       <c r="B180" s="7"/>
       <c r="C180" s="7"/>
@@ -3636,7 +3643,7 @@
     <row r="181" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="7">
         <f t="shared" si="9"/>
-        <v>1538500</v>
+        <v>1583500</v>
       </c>
       <c r="B181" s="7"/>
       <c r="C181" s="7"/>
@@ -3646,7 +3653,7 @@
     <row r="182" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="7">
         <f t="shared" si="9"/>
-        <v>1538500</v>
+        <v>1583500</v>
       </c>
       <c r="B182" s="7"/>
       <c r="C182" s="7"/>
@@ -3656,7 +3663,7 @@
     <row r="183" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="7">
         <f t="shared" si="9"/>
-        <v>1538500</v>
+        <v>1583500</v>
       </c>
       <c r="B183" s="7"/>
       <c r="C183" s="7"/>
@@ -3666,7 +3673,7 @@
     <row r="184" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="7">
         <f t="shared" si="9"/>
-        <v>1538500</v>
+        <v>1583500</v>
       </c>
       <c r="B184" s="7"/>
       <c r="C184" s="7"/>
@@ -3677,7 +3684,7 @@
       <c r="A185" s="8"/>
       <c r="B185" s="8">
         <f>SUM(B165:B184)+B159</f>
-        <v>13953500</v>
+        <v>13998500</v>
       </c>
       <c r="C185" s="8">
         <f>SUM(C165:C184)+C159</f>
@@ -3689,7 +3696,7 @@
     <row r="187" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B187" s="11">
         <f>A184</f>
-        <v>1538500</v>
+        <v>1583500</v>
       </c>
       <c r="C187" s="14" t="s">
         <v>183</v>

--- a/customers/mohammad javad.xlsx
+++ b/customers/mohammad javad.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="207">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -651,6 +651,15 @@
   </si>
   <si>
     <t>آب</t>
+  </si>
+  <si>
+    <t>1405/07/21</t>
+  </si>
+  <si>
+    <t>تنباکو</t>
+  </si>
+  <si>
+    <t>کمپوت ابمیو</t>
   </si>
 </sst>
 </file>
@@ -1177,7 +1186,7 @@
       </c>
       <c r="H2" s="8">
         <f>B187</f>
-        <v>1583500</v>
+        <v>2363500</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3513,27 +3522,37 @@
     <row r="168" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="7">
         <f>A167+B168-C168</f>
-        <v>1583500</v>
-      </c>
-      <c r="B168" s="7"/>
+        <v>1833500</v>
+      </c>
+      <c r="B168" s="7">
+        <v>250000</v>
+      </c>
       <c r="C168" s="7"/>
-      <c r="D168" s="7"/>
-      <c r="E168" s="1"/>
+      <c r="D168" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="169" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="7">
         <f>A168+B169-C169</f>
-        <v>1583500</v>
-      </c>
-      <c r="B169" s="7"/>
+        <v>2363500</v>
+      </c>
+      <c r="B169" s="7">
+        <v>530000</v>
+      </c>
       <c r="C169" s="7"/>
-      <c r="D169" s="7"/>
+      <c r="D169" s="7" t="s">
+        <v>206</v>
+      </c>
       <c r="E169" s="1"/>
     </row>
     <row r="170" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="7">
         <f t="shared" ref="A170" si="8">A169+B170-C170</f>
-        <v>1583500</v>
+        <v>2363500</v>
       </c>
       <c r="B170" s="7"/>
       <c r="C170" s="7"/>
@@ -3543,7 +3562,7 @@
     <row r="171" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="7">
         <f>A170+B171-C171</f>
-        <v>1583500</v>
+        <v>2363500</v>
       </c>
       <c r="B171" s="7"/>
       <c r="C171" s="7"/>
@@ -3553,7 +3572,7 @@
     <row r="172" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="7">
         <f t="shared" ref="A172:A184" si="9">A171+B172-C172</f>
-        <v>1583500</v>
+        <v>2363500</v>
       </c>
       <c r="B172" s="7"/>
       <c r="C172" s="7"/>
@@ -3563,7 +3582,7 @@
     <row r="173" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="7">
         <f t="shared" si="9"/>
-        <v>1583500</v>
+        <v>2363500</v>
       </c>
       <c r="B173" s="7"/>
       <c r="C173" s="7"/>
@@ -3573,7 +3592,7 @@
     <row r="174" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="7">
         <f t="shared" si="9"/>
-        <v>1583500</v>
+        <v>2363500</v>
       </c>
       <c r="B174" s="7"/>
       <c r="C174" s="7"/>
@@ -3583,7 +3602,7 @@
     <row r="175" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="7">
         <f t="shared" si="9"/>
-        <v>1583500</v>
+        <v>2363500</v>
       </c>
       <c r="B175" s="7"/>
       <c r="C175" s="7"/>
@@ -3593,7 +3612,7 @@
     <row r="176" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="7">
         <f t="shared" si="9"/>
-        <v>1583500</v>
+        <v>2363500</v>
       </c>
       <c r="B176" s="7"/>
       <c r="C176" s="7"/>
@@ -3603,7 +3622,7 @@
     <row r="177" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="7">
         <f t="shared" si="9"/>
-        <v>1583500</v>
+        <v>2363500</v>
       </c>
       <c r="B177" s="7"/>
       <c r="C177" s="7"/>
@@ -3613,7 +3632,7 @@
     <row r="178" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="7">
         <f t="shared" si="9"/>
-        <v>1583500</v>
+        <v>2363500</v>
       </c>
       <c r="B178" s="7"/>
       <c r="C178" s="7"/>
@@ -3623,7 +3642,7 @@
     <row r="179" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="7">
         <f t="shared" si="9"/>
-        <v>1583500</v>
+        <v>2363500</v>
       </c>
       <c r="B179" s="7"/>
       <c r="C179" s="7"/>
@@ -3633,7 +3652,7 @@
     <row r="180" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="7">
         <f t="shared" si="9"/>
-        <v>1583500</v>
+        <v>2363500</v>
       </c>
       <c r="B180" s="7"/>
       <c r="C180" s="7"/>
@@ -3643,7 +3662,7 @@
     <row r="181" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="7">
         <f t="shared" si="9"/>
-        <v>1583500</v>
+        <v>2363500</v>
       </c>
       <c r="B181" s="7"/>
       <c r="C181" s="7"/>
@@ -3653,7 +3672,7 @@
     <row r="182" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="7">
         <f t="shared" si="9"/>
-        <v>1583500</v>
+        <v>2363500</v>
       </c>
       <c r="B182" s="7"/>
       <c r="C182" s="7"/>
@@ -3663,7 +3682,7 @@
     <row r="183" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="7">
         <f t="shared" si="9"/>
-        <v>1583500</v>
+        <v>2363500</v>
       </c>
       <c r="B183" s="7"/>
       <c r="C183" s="7"/>
@@ -3673,7 +3692,7 @@
     <row r="184" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="7">
         <f t="shared" si="9"/>
-        <v>1583500</v>
+        <v>2363500</v>
       </c>
       <c r="B184" s="7"/>
       <c r="C184" s="7"/>
@@ -3684,7 +3703,7 @@
       <c r="A185" s="8"/>
       <c r="B185" s="8">
         <f>SUM(B165:B184)+B159</f>
-        <v>13998500</v>
+        <v>14778500</v>
       </c>
       <c r="C185" s="8">
         <f>SUM(C165:C184)+C159</f>
@@ -3696,7 +3715,7 @@
     <row r="187" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B187" s="11">
         <f>A184</f>
-        <v>1583500</v>
+        <v>2363500</v>
       </c>
       <c r="C187" s="14" t="s">
         <v>183</v>

--- a/customers/mohammad javad.xlsx
+++ b/customers/mohammad javad.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="209">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -660,6 +660,12 @@
   </si>
   <si>
     <t>کمپوت ابمیو</t>
+  </si>
+  <si>
+    <t>1405/07/23</t>
+  </si>
+  <si>
+    <t>دنگ مزه پل دو آب</t>
   </si>
 </sst>
 </file>
@@ -1186,7 +1192,7 @@
       </c>
       <c r="H2" s="8">
         <f>B187</f>
-        <v>2363500</v>
+        <v>2552500</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3552,17 +3558,23 @@
     <row r="170" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="7">
         <f t="shared" ref="A170" si="8">A169+B170-C170</f>
-        <v>2363500</v>
-      </c>
-      <c r="B170" s="7"/>
+        <v>2552500</v>
+      </c>
+      <c r="B170" s="7">
+        <v>189000</v>
+      </c>
       <c r="C170" s="7"/>
-      <c r="D170" s="7"/>
-      <c r="E170" s="1"/>
+      <c r="D170" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="171" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="7">
         <f>A170+B171-C171</f>
-        <v>2363500</v>
+        <v>2552500</v>
       </c>
       <c r="B171" s="7"/>
       <c r="C171" s="7"/>
@@ -3572,7 +3584,7 @@
     <row r="172" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="7">
         <f t="shared" ref="A172:A184" si="9">A171+B172-C172</f>
-        <v>2363500</v>
+        <v>2552500</v>
       </c>
       <c r="B172" s="7"/>
       <c r="C172" s="7"/>
@@ -3582,7 +3594,7 @@
     <row r="173" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="7">
         <f t="shared" si="9"/>
-        <v>2363500</v>
+        <v>2552500</v>
       </c>
       <c r="B173" s="7"/>
       <c r="C173" s="7"/>
@@ -3592,7 +3604,7 @@
     <row r="174" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="7">
         <f t="shared" si="9"/>
-        <v>2363500</v>
+        <v>2552500</v>
       </c>
       <c r="B174" s="7"/>
       <c r="C174" s="7"/>
@@ -3602,7 +3614,7 @@
     <row r="175" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="7">
         <f t="shared" si="9"/>
-        <v>2363500</v>
+        <v>2552500</v>
       </c>
       <c r="B175" s="7"/>
       <c r="C175" s="7"/>
@@ -3612,7 +3624,7 @@
     <row r="176" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="7">
         <f t="shared" si="9"/>
-        <v>2363500</v>
+        <v>2552500</v>
       </c>
       <c r="B176" s="7"/>
       <c r="C176" s="7"/>
@@ -3622,7 +3634,7 @@
     <row r="177" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="7">
         <f t="shared" si="9"/>
-        <v>2363500</v>
+        <v>2552500</v>
       </c>
       <c r="B177" s="7"/>
       <c r="C177" s="7"/>
@@ -3632,7 +3644,7 @@
     <row r="178" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="7">
         <f t="shared" si="9"/>
-        <v>2363500</v>
+        <v>2552500</v>
       </c>
       <c r="B178" s="7"/>
       <c r="C178" s="7"/>
@@ -3642,7 +3654,7 @@
     <row r="179" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="7">
         <f t="shared" si="9"/>
-        <v>2363500</v>
+        <v>2552500</v>
       </c>
       <c r="B179" s="7"/>
       <c r="C179" s="7"/>
@@ -3652,7 +3664,7 @@
     <row r="180" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="7">
         <f t="shared" si="9"/>
-        <v>2363500</v>
+        <v>2552500</v>
       </c>
       <c r="B180" s="7"/>
       <c r="C180" s="7"/>
@@ -3662,7 +3674,7 @@
     <row r="181" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="7">
         <f t="shared" si="9"/>
-        <v>2363500</v>
+        <v>2552500</v>
       </c>
       <c r="B181" s="7"/>
       <c r="C181" s="7"/>
@@ -3672,7 +3684,7 @@
     <row r="182" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="7">
         <f t="shared" si="9"/>
-        <v>2363500</v>
+        <v>2552500</v>
       </c>
       <c r="B182" s="7"/>
       <c r="C182" s="7"/>
@@ -3682,7 +3694,7 @@
     <row r="183" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="7">
         <f t="shared" si="9"/>
-        <v>2363500</v>
+        <v>2552500</v>
       </c>
       <c r="B183" s="7"/>
       <c r="C183" s="7"/>
@@ -3692,7 +3704,7 @@
     <row r="184" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="7">
         <f t="shared" si="9"/>
-        <v>2363500</v>
+        <v>2552500</v>
       </c>
       <c r="B184" s="7"/>
       <c r="C184" s="7"/>
@@ -3703,7 +3715,7 @@
       <c r="A185" s="8"/>
       <c r="B185" s="8">
         <f>SUM(B165:B184)+B159</f>
-        <v>14778500</v>
+        <v>14967500</v>
       </c>
       <c r="C185" s="8">
         <f>SUM(C165:C184)+C159</f>
@@ -3715,7 +3727,7 @@
     <row r="187" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B187" s="11">
         <f>A184</f>
-        <v>2363500</v>
+        <v>2552500</v>
       </c>
       <c r="C187" s="14" t="s">
         <v>183</v>

--- a/customers/mohammad javad.xlsx
+++ b/customers/mohammad javad.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="211">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -666,6 +666,12 @@
   </si>
   <si>
     <t>دنگ مزه پل دو آب</t>
+  </si>
+  <si>
+    <t>1405/07/30</t>
+  </si>
+  <si>
+    <t>پفک قهوه</t>
   </si>
 </sst>
 </file>
@@ -1192,7 +1198,7 @@
       </c>
       <c r="H2" s="8">
         <f>B187</f>
-        <v>2552500</v>
+        <v>2702500</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3574,17 +3580,23 @@
     <row r="171" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="7">
         <f>A170+B171-C171</f>
-        <v>2552500</v>
-      </c>
-      <c r="B171" s="7"/>
+        <v>2702500</v>
+      </c>
+      <c r="B171" s="7">
+        <v>150000</v>
+      </c>
       <c r="C171" s="7"/>
-      <c r="D171" s="7"/>
-      <c r="E171" s="1"/>
+      <c r="D171" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="172" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="7">
         <f t="shared" ref="A172:A184" si="9">A171+B172-C172</f>
-        <v>2552500</v>
+        <v>2702500</v>
       </c>
       <c r="B172" s="7"/>
       <c r="C172" s="7"/>
@@ -3594,7 +3606,7 @@
     <row r="173" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="7">
         <f t="shared" si="9"/>
-        <v>2552500</v>
+        <v>2702500</v>
       </c>
       <c r="B173" s="7"/>
       <c r="C173" s="7"/>
@@ -3604,7 +3616,7 @@
     <row r="174" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="7">
         <f t="shared" si="9"/>
-        <v>2552500</v>
+        <v>2702500</v>
       </c>
       <c r="B174" s="7"/>
       <c r="C174" s="7"/>
@@ -3614,7 +3626,7 @@
     <row r="175" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="7">
         <f t="shared" si="9"/>
-        <v>2552500</v>
+        <v>2702500</v>
       </c>
       <c r="B175" s="7"/>
       <c r="C175" s="7"/>
@@ -3624,7 +3636,7 @@
     <row r="176" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="7">
         <f t="shared" si="9"/>
-        <v>2552500</v>
+        <v>2702500</v>
       </c>
       <c r="B176" s="7"/>
       <c r="C176" s="7"/>
@@ -3634,7 +3646,7 @@
     <row r="177" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="7">
         <f t="shared" si="9"/>
-        <v>2552500</v>
+        <v>2702500</v>
       </c>
       <c r="B177" s="7"/>
       <c r="C177" s="7"/>
@@ -3644,7 +3656,7 @@
     <row r="178" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="7">
         <f t="shared" si="9"/>
-        <v>2552500</v>
+        <v>2702500</v>
       </c>
       <c r="B178" s="7"/>
       <c r="C178" s="7"/>
@@ -3654,7 +3666,7 @@
     <row r="179" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="7">
         <f t="shared" si="9"/>
-        <v>2552500</v>
+        <v>2702500</v>
       </c>
       <c r="B179" s="7"/>
       <c r="C179" s="7"/>
@@ -3664,7 +3676,7 @@
     <row r="180" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="7">
         <f t="shared" si="9"/>
-        <v>2552500</v>
+        <v>2702500</v>
       </c>
       <c r="B180" s="7"/>
       <c r="C180" s="7"/>
@@ -3674,7 +3686,7 @@
     <row r="181" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="7">
         <f t="shared" si="9"/>
-        <v>2552500</v>
+        <v>2702500</v>
       </c>
       <c r="B181" s="7"/>
       <c r="C181" s="7"/>
@@ -3684,7 +3696,7 @@
     <row r="182" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="7">
         <f t="shared" si="9"/>
-        <v>2552500</v>
+        <v>2702500</v>
       </c>
       <c r="B182" s="7"/>
       <c r="C182" s="7"/>
@@ -3694,7 +3706,7 @@
     <row r="183" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="7">
         <f t="shared" si="9"/>
-        <v>2552500</v>
+        <v>2702500</v>
       </c>
       <c r="B183" s="7"/>
       <c r="C183" s="7"/>
@@ -3704,7 +3716,7 @@
     <row r="184" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="7">
         <f t="shared" si="9"/>
-        <v>2552500</v>
+        <v>2702500</v>
       </c>
       <c r="B184" s="7"/>
       <c r="C184" s="7"/>
@@ -3715,7 +3727,7 @@
       <c r="A185" s="8"/>
       <c r="B185" s="8">
         <f>SUM(B165:B184)+B159</f>
-        <v>14967500</v>
+        <v>15117500</v>
       </c>
       <c r="C185" s="8">
         <f>SUM(C165:C184)+C159</f>
@@ -3727,7 +3739,7 @@
     <row r="187" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B187" s="11">
         <f>A184</f>
-        <v>2552500</v>
+        <v>2702500</v>
       </c>
       <c r="C187" s="14" t="s">
         <v>183</v>

--- a/customers/mohammad javad.xlsx
+++ b/customers/mohammad javad.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="212">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -672,6 +672,9 @@
   </si>
   <si>
     <t>پفک قهوه</t>
+  </si>
+  <si>
+    <t>1405/08/05</t>
   </si>
 </sst>
 </file>
@@ -1198,7 +1201,7 @@
       </c>
       <c r="H2" s="8">
         <f>B187</f>
-        <v>2702500</v>
+        <v>1202500</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3596,17 +3599,23 @@
     <row r="172" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="7">
         <f t="shared" ref="A172:A184" si="9">A171+B172-C172</f>
-        <v>2702500</v>
+        <v>1202500</v>
       </c>
       <c r="B172" s="7"/>
-      <c r="C172" s="7"/>
-      <c r="D172" s="7"/>
-      <c r="E172" s="1"/>
+      <c r="C172" s="7">
+        <v>1500000</v>
+      </c>
+      <c r="D172" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="173" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="7">
         <f t="shared" si="9"/>
-        <v>2702500</v>
+        <v>1202500</v>
       </c>
       <c r="B173" s="7"/>
       <c r="C173" s="7"/>
@@ -3616,7 +3625,7 @@
     <row r="174" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="7">
         <f t="shared" si="9"/>
-        <v>2702500</v>
+        <v>1202500</v>
       </c>
       <c r="B174" s="7"/>
       <c r="C174" s="7"/>
@@ -3626,7 +3635,7 @@
     <row r="175" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="7">
         <f t="shared" si="9"/>
-        <v>2702500</v>
+        <v>1202500</v>
       </c>
       <c r="B175" s="7"/>
       <c r="C175" s="7"/>
@@ -3636,7 +3645,7 @@
     <row r="176" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="7">
         <f t="shared" si="9"/>
-        <v>2702500</v>
+        <v>1202500</v>
       </c>
       <c r="B176" s="7"/>
       <c r="C176" s="7"/>
@@ -3646,7 +3655,7 @@
     <row r="177" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="7">
         <f t="shared" si="9"/>
-        <v>2702500</v>
+        <v>1202500</v>
       </c>
       <c r="B177" s="7"/>
       <c r="C177" s="7"/>
@@ -3656,7 +3665,7 @@
     <row r="178" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="7">
         <f t="shared" si="9"/>
-        <v>2702500</v>
+        <v>1202500</v>
       </c>
       <c r="B178" s="7"/>
       <c r="C178" s="7"/>
@@ -3666,7 +3675,7 @@
     <row r="179" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="7">
         <f t="shared" si="9"/>
-        <v>2702500</v>
+        <v>1202500</v>
       </c>
       <c r="B179" s="7"/>
       <c r="C179" s="7"/>
@@ -3676,7 +3685,7 @@
     <row r="180" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="7">
         <f t="shared" si="9"/>
-        <v>2702500</v>
+        <v>1202500</v>
       </c>
       <c r="B180" s="7"/>
       <c r="C180" s="7"/>
@@ -3686,7 +3695,7 @@
     <row r="181" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="7">
         <f t="shared" si="9"/>
-        <v>2702500</v>
+        <v>1202500</v>
       </c>
       <c r="B181" s="7"/>
       <c r="C181" s="7"/>
@@ -3696,7 +3705,7 @@
     <row r="182" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="7">
         <f t="shared" si="9"/>
-        <v>2702500</v>
+        <v>1202500</v>
       </c>
       <c r="B182" s="7"/>
       <c r="C182" s="7"/>
@@ -3706,7 +3715,7 @@
     <row r="183" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="7">
         <f t="shared" si="9"/>
-        <v>2702500</v>
+        <v>1202500</v>
       </c>
       <c r="B183" s="7"/>
       <c r="C183" s="7"/>
@@ -3716,7 +3725,7 @@
     <row r="184" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="7">
         <f t="shared" si="9"/>
-        <v>2702500</v>
+        <v>1202500</v>
       </c>
       <c r="B184" s="7"/>
       <c r="C184" s="7"/>
@@ -3731,7 +3740,7 @@
       </c>
       <c r="C185" s="8">
         <f>SUM(C165:C184)+C159</f>
-        <v>12415000</v>
+        <v>13915000</v>
       </c>
       <c r="D185" s="8"/>
     </row>
@@ -3739,7 +3748,7 @@
     <row r="187" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B187" s="11">
         <f>A184</f>
-        <v>2702500</v>
+        <v>1202500</v>
       </c>
       <c r="C187" s="14" t="s">
         <v>183</v>

--- a/customers/mohammad javad.xlsx
+++ b/customers/mohammad javad.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="214">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -675,6 +675,12 @@
   </si>
   <si>
     <t>1405/08/05</t>
+  </si>
+  <si>
+    <t>1405/08/09</t>
+  </si>
+  <si>
+    <t>وجه برگه سفته</t>
   </si>
 </sst>
 </file>
@@ -1201,7 +1207,7 @@
       </c>
       <c r="H2" s="8">
         <f>B187</f>
-        <v>1202500</v>
+        <v>762500</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3615,17 +3621,23 @@
     <row r="173" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="7">
         <f t="shared" si="9"/>
-        <v>1202500</v>
+        <v>762500</v>
       </c>
       <c r="B173" s="7"/>
-      <c r="C173" s="7"/>
-      <c r="D173" s="7"/>
-      <c r="E173" s="1"/>
+      <c r="C173" s="7">
+        <v>440000</v>
+      </c>
+      <c r="D173" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="174" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="7">
         <f t="shared" si="9"/>
-        <v>1202500</v>
+        <v>762500</v>
       </c>
       <c r="B174" s="7"/>
       <c r="C174" s="7"/>
@@ -3635,7 +3647,7 @@
     <row r="175" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="7">
         <f t="shared" si="9"/>
-        <v>1202500</v>
+        <v>762500</v>
       </c>
       <c r="B175" s="7"/>
       <c r="C175" s="7"/>
@@ -3645,7 +3657,7 @@
     <row r="176" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="7">
         <f t="shared" si="9"/>
-        <v>1202500</v>
+        <v>762500</v>
       </c>
       <c r="B176" s="7"/>
       <c r="C176" s="7"/>
@@ -3655,7 +3667,7 @@
     <row r="177" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="7">
         <f t="shared" si="9"/>
-        <v>1202500</v>
+        <v>762500</v>
       </c>
       <c r="B177" s="7"/>
       <c r="C177" s="7"/>
@@ -3665,7 +3677,7 @@
     <row r="178" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="7">
         <f t="shared" si="9"/>
-        <v>1202500</v>
+        <v>762500</v>
       </c>
       <c r="B178" s="7"/>
       <c r="C178" s="7"/>
@@ -3675,7 +3687,7 @@
     <row r="179" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="7">
         <f t="shared" si="9"/>
-        <v>1202500</v>
+        <v>762500</v>
       </c>
       <c r="B179" s="7"/>
       <c r="C179" s="7"/>
@@ -3685,7 +3697,7 @@
     <row r="180" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="7">
         <f t="shared" si="9"/>
-        <v>1202500</v>
+        <v>762500</v>
       </c>
       <c r="B180" s="7"/>
       <c r="C180" s="7"/>
@@ -3695,7 +3707,7 @@
     <row r="181" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="7">
         <f t="shared" si="9"/>
-        <v>1202500</v>
+        <v>762500</v>
       </c>
       <c r="B181" s="7"/>
       <c r="C181" s="7"/>
@@ -3705,7 +3717,7 @@
     <row r="182" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="7">
         <f t="shared" si="9"/>
-        <v>1202500</v>
+        <v>762500</v>
       </c>
       <c r="B182" s="7"/>
       <c r="C182" s="7"/>
@@ -3715,7 +3727,7 @@
     <row r="183" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="7">
         <f t="shared" si="9"/>
-        <v>1202500</v>
+        <v>762500</v>
       </c>
       <c r="B183" s="7"/>
       <c r="C183" s="7"/>
@@ -3725,7 +3737,7 @@
     <row r="184" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="7">
         <f t="shared" si="9"/>
-        <v>1202500</v>
+        <v>762500</v>
       </c>
       <c r="B184" s="7"/>
       <c r="C184" s="7"/>
@@ -3740,7 +3752,7 @@
       </c>
       <c r="C185" s="8">
         <f>SUM(C165:C184)+C159</f>
-        <v>13915000</v>
+        <v>14355000</v>
       </c>
       <c r="D185" s="8"/>
     </row>
@@ -3748,7 +3760,7 @@
     <row r="187" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B187" s="11">
         <f>A184</f>
-        <v>1202500</v>
+        <v>762500</v>
       </c>
       <c r="C187" s="14" t="s">
         <v>183</v>
